--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -194,19 +194,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>横=通路组(按疾病分类) · 纵=市值前30家药企 · 格子=靶点+行业地位 ｜ ★首创FIC ◆领跑BIC ●重要 ○在研 ｜ 红色加粗=当下最热但尚未攻克/未成熟的前沿靶点 ｜ 市值截至2026-07</t>
+          <t>横=通路组(按疾病分类) · 纵=市值前30家药企 · 每格每个靶点单独一行 ｜ ★首创FIC ◆领跑BIC ●重要 ○在研 ｜ 红色加粗=当下最热但尚未攻克/未成熟的前沿靶点 ｜ 市值截至2026-07</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>01 Eli Lilly · 🇺🇸 LLY</t>
@@ -786,7 +786,8 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>RET★·BTK●</t>
+          <t>RET★
+BTK●</t>
         </is>
       </c>
       <c r="C5" s="13" t="n"/>
@@ -800,7 +801,8 @@
       <c r="G5" s="13" t="n"/>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>IL-13●·IL-23●</t>
+          <t>IL-13●
+IL-23●</t>
         </is>
       </c>
       <c r="I5" s="13" t="n"/>
@@ -855,7 +857,7 @@
       <c r="V5" s="13" t="n"/>
       <c r="W5" s="13" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>02 Johnson &amp; Johnson · 🇺🇸 JNJ</t>
@@ -863,7 +865,8 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>BTK★·EGFR×MET★</t>
+          <t>BTK★
+EGFR×MET★</t>
         </is>
       </c>
       <c r="C6" s="13" t="n"/>
@@ -878,7 +881,8 @@
               <color rgb="002E463E"/>
               <sz val="8.5"/>
             </rPr>
-            <t>CD38◆·BCMA/</t>
+            <t>CD38◆
+BCMA/</t>
           </r>
           <r>
             <rPr>
@@ -901,7 +905,8 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>IL-12/23★·IL-23●</t>
+          <t>IL-12/23★
+IL-23●</t>
         </is>
       </c>
       <c r="I6" s="13" t="n"/>
@@ -914,7 +919,8 @@
       <c r="P6" s="13" t="n"/>
       <c r="Q6" s="12" t="inlineStr">
         <is>
-          <t>NMDA★·D2◆</t>
+          <t>NMDA★
+D2◆</t>
         </is>
       </c>
       <c r="R6" s="13" t="n"/>
@@ -924,7 +930,7 @@
       <c r="V6" s="13" t="n"/>
       <c r="W6" s="13" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>03 AbbVie · 🇺🇸 ABBV</t>
@@ -946,7 +952,8 @@
       <c r="G7" s="13" t="n"/>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>TNF◆·IL-23◆</t>
+          <t>TNF◆
+IL-23◆</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
@@ -973,7 +980,7 @@
       <c r="V7" s="13" t="n"/>
       <c r="W7" s="13" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>04 Roche（含基因泰克）· 🇨🇭 RO</t>
@@ -981,7 +988,8 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>HER2★·BRAF●</t>
+          <t>HER2★
+BRAF●</t>
         </is>
       </c>
       <c r="C8" s="13" t="n"/>
@@ -994,7 +1002,8 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>CD20★·HER2-ADC●</t>
+          <t>CD20★
+HER2-ADC●</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -1026,7 +1035,7 @@
       <c r="V8" s="13" t="n"/>
       <c r="W8" s="13" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>05 Merck / MSD · 🇺🇸 MRK</t>
@@ -1048,7 +1057,8 @@
       <c r="K9" s="13" t="n"/>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>他汀★·口服PCSK9○</t>
+          <t>他汀★
+口服PCSK9○</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
@@ -1067,7 +1077,7 @@
       <c r="V9" s="13" t="n"/>
       <c r="W9" s="13" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>06 Novartis · 🇨🇭 NVS</t>
@@ -1075,7 +1085,8 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>BCR-ABL★·BRAF/MEK●</t>
+          <t>BCR-ABL★
+BRAF/MEK●</t>
         </is>
       </c>
       <c r="C10" s="13" t="n"/>
@@ -1088,12 +1099,14 @@
       <c r="F10" s="13" t="n"/>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>CD19 CAR-T★·放射配体◆</t>
+          <t>CD19 CAR-T★
+放射配体◆</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>IL-17★·IL-1β●</t>
+          <t>IL-17★
+IL-1β●</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -1124,7 +1137,7 @@
       <c r="V10" s="13" t="n"/>
       <c r="W10" s="13" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>07 AstraZeneca · 🇬🇧 AZN</t>
@@ -1132,7 +1145,8 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>EGFR◆·BTK●</t>
+          <t>EGFR◆
+BTK●</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1149,12 +1163,14 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>HER2-ADC◆·TROP2●</t>
+          <t>HER2-ADC◆
+TROP2●</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>TSLP★·IL-5●</t>
+          <t>TSLP★
+IL-5●</t>
         </is>
       </c>
       <c r="I11" s="13" t="n"/>
@@ -1177,7 +1193,7 @@
       <c r="V11" s="13" t="n"/>
       <c r="W11" s="13" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>08 Novo Nordisk · 🇩🇰 NVO</t>
@@ -1202,7 +1218,8 @@
               <color rgb="002E463E"/>
               <sz val="8.5"/>
             </rPr>
-            <t>GLP-1◆·</t>
+            <t xml:space="preserve">GLP-1◆
+</t>
           </r>
           <r>
             <rPr>
@@ -1242,7 +1259,7 @@
       <c r="V12" s="13" t="n"/>
       <c r="W12" s="13" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>09 Amgen · 🇺🇸 AMGN</t>
@@ -1281,7 +1298,8 @@
               <color rgb="002E463E"/>
               <sz val="8.5"/>
             </rPr>
-            <t>CD19-BiTE★·</t>
+            <t xml:space="preserve">CD19-BiTE★
+</t>
           </r>
           <r>
             <rPr>
@@ -1335,7 +1353,7 @@
       <c r="V13" s="13" t="n"/>
       <c r="W13" s="13" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
           <t>10 Gilead · 🇺🇸 GILD</t>
@@ -1348,7 +1366,8 @@
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>TROP2-ADC★·CD19 CAR-T◆</t>
+          <t>TROP2-ADC★
+CD19 CAR-T◆</t>
         </is>
       </c>
       <c r="H14" s="13" t="n"/>
@@ -1421,7 +1440,7 @@
       <c r="V15" s="13" t="n"/>
       <c r="W15" s="13" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="47" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
           <t>13 Bristol Myers Squibb · 🇺🇸 BMY</t>
@@ -1433,7 +1452,9 @@
       <c r="E16" s="13" t="n"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>CTLA-4★·PD-1●·LAG-3★</t>
+          <t>CTLA-4★
+PD-1●
+LAG-3★</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -1732,7 +1753,7 @@
       <c r="V22" s="13" t="n"/>
       <c r="W22" s="13" t="n"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="34" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>20 UCB · 🇧🇪 UCB</t>
@@ -1746,7 +1767,8 @@
       <c r="G23" s="13" t="n"/>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>IL-17A/F★·TNF●</t>
+          <t>IL-17A/F★
+TNF●</t>
         </is>
       </c>
       <c r="I23" s="13" t="n"/>
@@ -1892,7 +1914,7 @@
       <c r="V26" s="13" t="n"/>
       <c r="W26" s="13" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="34" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>25 江苏恒瑞 · 🇨🇳 600276</t>
@@ -1900,7 +1922,8 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>VEGFR2●·HER2●</t>
+          <t>VEGFR2●
+HER2●</t>
         </is>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -2218,26 +2241,33 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟的前沿：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+          <t>· 每个格子里，同一公司在该通路上的多个靶点已各自单独成行。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>· 仅标注有重大布局的靶点（非全管线）；通路列沿用本站「通路词典」的分区。</t>
+          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟的前沿：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>· 不属于这些通路组的重磅（疫苗 / HIV·HCV / 抗凝 / 眼科VEGF / 前列腺激素 / EPO·G-CSF / 骨·医美）未在表中，详见「公司词典」。</t>
+          <t>· 仅标注有重大布局的靶点（非全管线）；通路列沿用本站「通路词典」的分区。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>· 不属于这些通路组的重磅（疫苗 / HIV·HCV / 抗凝 / 眼科VEGF / 前列腺激素 / EPO·G-CSF / 骨·医美）未在表中，详见「公司词典」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>· 已剔除市值榜中的非研发型公司：CVS Health(第12·PBM)、WuXi药明康德(第23·CRO)、Lonza(第27·CDMO)；Sandoz为生物类似药商，整行留空。</t>
         </is>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -45,14 +45,14 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002E463E"/>
-      <sz val="8.5"/>
+      <color rgb="00173029"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00173029"/>
-      <sz val="9"/>
+      <color rgb="002E463E"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -70,12 +70,17 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDE4"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -104,17 +109,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDE4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAFAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -164,20 +169,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -187,25 +192,31 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,11 +586,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:X41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14.5" customWidth="1" min="3" max="3"/>
     <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="14.5" customWidth="1" min="5" max="5"/>
@@ -601,6 +612,7 @@
     <col width="14.5" customWidth="1" min="21" max="21"/>
     <col width="14.5" customWidth="1" min="22" max="22"/>
     <col width="14.5" customWidth="1" min="23" max="23"/>
+    <col width="14.5" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -613,7 +625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>横=通路组(按疾病分类) · 纵=市值前30家药企 · 每格每个靶点单独一行 ｜ ★首创FIC ◆领跑BIC ●重要 ○在研 ｜ 红色加粗=当下最热但尚未攻克/未成熟的前沿靶点 ｜ 市值截至2026-07</t>
+          <t>横=通路组 · 纵=市值前30家药企 · 公司后设「★◆●计数」列 · 每格每个靶点单独一行 ｜ ★首创FIC ◆领跑BIC ●重要 ○在研 ｜ 红色加粗=最热但未攻克前沿 ｜ 市值截至2026-07</t>
         </is>
       </c>
     </row>
@@ -625,190 +637,228 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>★◆● 计数</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
           <t>肿瘤 Oncology</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>免疫炎症 Immunology</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>代谢 Metabolic</t>
         </is>
       </c>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="N3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>神经 CNS</t>
         </is>
       </c>
-      <c r="P3" s="5" t="n"/>
-      <c r="Q3" s="5" t="n"/>
-      <c r="R3" s="5" t="n"/>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="6" t="n"/>
+      <c r="T3" s="10" t="inlineStr">
         <is>
           <t>罕见/遗传 Rare</t>
         </is>
       </c>
-      <c r="T3" s="5" t="n"/>
-      <c r="U3" s="5" t="n"/>
-      <c r="V3" s="5" t="n"/>
-      <c r="W3" s="5" t="n"/>
+      <c r="U3" s="6" t="n"/>
+      <c r="V3" s="6" t="n"/>
+      <c r="W3" s="6" t="n"/>
+      <c r="X3" s="6" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="B4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>驱动激酶/突变</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>合成致死</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>周期/凋亡</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>表观/转录</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>免疫检查点</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>表面投送/ADC/CAR-T</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>细胞因子(抗体)</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>胞内信号(小分子)</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>细胞/受体</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>FcRn/自免细胞</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>血脂</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>肥胖/糖尿</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>MASH</t>
         </is>
       </c>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>神经退行</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>疼痛/偏头痛</t>
         </is>
       </c>
-      <c r="Q4" s="10" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>精神</t>
         </is>
       </c>
-      <c r="R4" s="10" t="inlineStr">
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>递送/癫痫</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>替代/矫正</t>
         </is>
       </c>
-      <c r="T4" s="10" t="inlineStr">
+      <c r="U4" s="11" t="inlineStr">
         <is>
           <t>关基因(RNA)</t>
         </is>
       </c>
-      <c r="U4" s="10" t="inlineStr">
+      <c r="V4" s="11" t="inlineStr">
         <is>
           <t>补基因</t>
         </is>
       </c>
-      <c r="V4" s="10" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>改基因(编辑)</t>
         </is>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="X4" s="11" t="inlineStr">
         <is>
           <t>补体/其它</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="5" ht="47" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>01 Eli Lilly · 🇺🇸 LLY</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>RET★
 BTK●</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>CDK4/6◆</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>IL-13●
 IL-23●</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
-      <c r="L5" s="16" t="inlineStr">
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -829,51 +879,84 @@
           </r>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t>双靶GLP-1◆</t>
         </is>
       </c>
-      <c r="N5" s="16" t="inlineStr">
+      <c r="O5" s="18" t="inlineStr">
         <is>
           <t>GLP-1○</t>
         </is>
       </c>
-      <c r="O5" s="15" t="inlineStr">
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t>Aβ●</t>
         </is>
       </c>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="12" t="inlineStr">
+      <c r="Q5" s="15" t="n"/>
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t>SSRI★</t>
         </is>
       </c>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="S5" s="15" t="n"/>
+      <c r="T5" s="15" t="n"/>
+      <c r="U5" s="15" t="n"/>
+      <c r="V5" s="15" t="n"/>
+      <c r="W5" s="15" t="n"/>
+      <c r="X5" s="15" t="n"/>
+    </row>
+    <row r="6" ht="47" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>02 Johnson &amp; Johnson · 🇺🇸 JNJ</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">4★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>BTK★
 EGFR×MET★</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -903,314 +986,512 @@
           </r>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>IL-12/23★
 IL-23●</t>
         </is>
       </c>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
-      <c r="L6" s="13" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
-      <c r="Q6" s="12" t="inlineStr">
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t>NMDA★
 D2◆</t>
         </is>
       </c>
-      <c r="R6" s="13" t="n"/>
-      <c r="S6" s="13" t="n"/>
-      <c r="T6" s="13" t="n"/>
-      <c r="U6" s="13" t="n"/>
-      <c r="V6" s="13" t="n"/>
-      <c r="W6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="S6" s="15" t="n"/>
+      <c r="T6" s="15" t="n"/>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="n"/>
+      <c r="W6" s="15" t="n"/>
+      <c r="X6" s="15" t="n"/>
+    </row>
+    <row r="7" ht="47" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>03 AbbVie · 🇺🇸 ABBV</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>BTK●</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>BCL-2★</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="13" t="n"/>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>TNF◆
 IL-23◆</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>JAK●</t>
         </is>
       </c>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
-      <c r="L7" s="13" t="n"/>
-      <c r="M7" s="13" t="n"/>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n"/>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="15" t="n"/>
+      <c r="Q7" s="17" t="inlineStr">
         <is>
           <t>CGRP●</t>
         </is>
       </c>
-      <c r="Q7" s="13" t="n"/>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n"/>
-      <c r="T7" s="13" t="n"/>
-      <c r="U7" s="13" t="n"/>
-      <c r="V7" s="13" t="n"/>
-      <c r="W7" s="13" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="R7" s="15" t="n"/>
+      <c r="S7" s="15" t="n"/>
+      <c r="T7" s="15" t="n"/>
+      <c r="U7" s="15" t="n"/>
+      <c r="V7" s="15" t="n"/>
+      <c r="W7" s="15" t="n"/>
+      <c r="X7" s="15" t="n"/>
+    </row>
+    <row r="8" ht="47" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>04 Roche（含基因泰克）· 🇨🇭 RO</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>HER2★
 BRAF●</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t>PD-L1●</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>CD20★
 HER2-ADC●</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>IL-6★</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
-      <c r="L8" s="13" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t>MS/CD20◆</t>
         </is>
       </c>
-      <c r="P8" s="13" t="n"/>
-      <c r="Q8" s="13" t="n"/>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n"/>
-      <c r="T8" s="13" t="n"/>
-      <c r="U8" s="14" t="inlineStr">
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="15" t="n"/>
+      <c r="S8" s="15" t="n"/>
+      <c r="T8" s="15" t="n"/>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="16" t="inlineStr">
         <is>
           <t>血友病·双抗◆</t>
         </is>
       </c>
-      <c r="V8" s="13" t="n"/>
-      <c r="W8" s="13" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="W8" s="15" t="n"/>
+      <c r="X8" s="15" t="n"/>
+    </row>
+    <row r="9" ht="47" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>05 Merck / MSD · 🇺🇸 MRK</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>PD-1◆</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t>他汀★
 口服PCSK9○</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t>DPP-4★</t>
         </is>
       </c>
-      <c r="N9" s="13" t="n"/>
-      <c r="O9" s="13" t="n"/>
-      <c r="P9" s="13" t="n"/>
-      <c r="Q9" s="13" t="n"/>
-      <c r="R9" s="13" t="n"/>
-      <c r="S9" s="13" t="n"/>
-      <c r="T9" s="13" t="n"/>
-      <c r="U9" s="13" t="n"/>
-      <c r="V9" s="13" t="n"/>
-      <c r="W9" s="13" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="15" t="n"/>
+      <c r="S9" s="15" t="n"/>
+      <c r="T9" s="15" t="n"/>
+      <c r="U9" s="15" t="n"/>
+      <c r="V9" s="15" t="n"/>
+      <c r="W9" s="15" t="n"/>
+      <c r="X9" s="15" t="n"/>
+    </row>
+    <row r="10" ht="47" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>06 Novartis · 🇨🇭 NVS</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>5●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>BCR-ABL★
 BRAF/MEK●</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>CDK4/6●</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>CD19 CAR-T★
 放射配体◆</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>IL-17★
 IL-1β●</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>S1P●</t>
         </is>
       </c>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
-      <c r="L10" s="15" t="inlineStr">
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>PCSK9-siRNA●</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
-      <c r="Q10" s="13" t="n"/>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n"/>
-      <c r="T10" s="13" t="n"/>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="n"/>
+      <c r="R10" s="15" t="n"/>
+      <c r="S10" s="15" t="n"/>
+      <c r="T10" s="15" t="n"/>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="16" t="inlineStr">
         <is>
           <t>SMA·AAV◆</t>
         </is>
       </c>
-      <c r="V10" s="13" t="n"/>
-      <c r="W10" s="13" t="n"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="W10" s="15" t="n"/>
+      <c r="X10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="47" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>07 AstraZeneca · 🇬🇧 AZN</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">4◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>4●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>EGFR◆
 BTK●</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>PARP◆</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>PD-L1●</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>HER2-ADC◆
 TROP2●</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>TSLP★
 IL-5●</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
-      <c r="L11" s="13" t="n"/>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>SGLT2◆</t>
         </is>
       </c>
-      <c r="N11" s="13" t="n"/>
-      <c r="O11" s="13" t="n"/>
-      <c r="P11" s="13" t="n"/>
-      <c r="Q11" s="13" t="n"/>
-      <c r="R11" s="13" t="n"/>
-      <c r="S11" s="13" t="n"/>
-      <c r="T11" s="13" t="n"/>
-      <c r="U11" s="13" t="n"/>
-      <c r="V11" s="13" t="n"/>
-      <c r="W11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="O11" s="15" t="n"/>
+      <c r="P11" s="15" t="n"/>
+      <c r="Q11" s="15" t="n"/>
+      <c r="R11" s="15" t="n"/>
+      <c r="S11" s="15" t="n"/>
+      <c r="T11" s="15" t="n"/>
+      <c r="U11" s="15" t="n"/>
+      <c r="V11" s="15" t="n"/>
+      <c r="W11" s="15" t="n"/>
+      <c r="X11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="47" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>08 Novo Nordisk · 🇩🇰 NVO</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
-      <c r="L12" s="13" t="n"/>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1240,32 +1521,65 @@
           </r>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="O12" s="17" t="inlineStr">
         <is>
           <t>GLP-1●</t>
         </is>
       </c>
-      <c r="O12" s="13" t="n"/>
-      <c r="P12" s="13" t="n"/>
-      <c r="Q12" s="13" t="n"/>
-      <c r="R12" s="13" t="n"/>
-      <c r="S12" s="13" t="n"/>
-      <c r="T12" s="13" t="n"/>
-      <c r="U12" s="15" t="inlineStr">
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="15" t="n"/>
+      <c r="S12" s="15" t="n"/>
+      <c r="T12" s="15" t="n"/>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="17" t="inlineStr">
         <is>
           <t>血友病●</t>
         </is>
       </c>
-      <c r="V12" s="13" t="n"/>
-      <c r="W12" s="13" t="n"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="W12" s="15" t="n"/>
+      <c r="X12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="47" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>09 Amgen · 🇺🇸 AMGN</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1286,11 +1600,11 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1320,190 +1634,322 @@
           </r>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>TNF●</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>PDE4●</t>
         </is>
       </c>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="16" t="inlineStr">
         <is>
           <t>PCSK9◆</t>
         </is>
       </c>
-      <c r="M13" s="13" t="n"/>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="13" t="n"/>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="15" t="n"/>
+      <c r="Q13" s="14" t="inlineStr">
         <is>
           <t>CGRP★</t>
         </is>
       </c>
-      <c r="Q13" s="13" t="n"/>
-      <c r="R13" s="13" t="n"/>
-      <c r="S13" s="13" t="n"/>
-      <c r="T13" s="13" t="n"/>
-      <c r="U13" s="13" t="n"/>
-      <c r="V13" s="13" t="n"/>
-      <c r="W13" s="13" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="R13" s="15" t="n"/>
+      <c r="S13" s="15" t="n"/>
+      <c r="T13" s="15" t="n"/>
+      <c r="U13" s="15" t="n"/>
+      <c r="V13" s="15" t="n"/>
+      <c r="W13" s="15" t="n"/>
+      <c r="X13" s="15" t="n"/>
+    </row>
+    <row r="14" ht="47" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>10 Gilead · 🇺🇸 GILD</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>TROP2-ADC★
 CD19 CAR-T◆</t>
         </is>
       </c>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
-      <c r="Q14" s="13" t="n"/>
-      <c r="R14" s="13" t="n"/>
-      <c r="S14" s="13" t="n"/>
-      <c r="T14" s="13" t="n"/>
-      <c r="U14" s="13" t="n"/>
-      <c r="V14" s="13" t="n"/>
-      <c r="W14" s="13" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="15" t="n"/>
+      <c r="S14" s="15" t="n"/>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n"/>
+      <c r="W14" s="15" t="n"/>
+      <c r="X14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="47" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>11 Pfizer · 🇺🇸 PFE</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>ALK★</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>CDK4/6★</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>BCMA●</t>
         </is>
       </c>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>JAK★</t>
         </is>
       </c>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>他汀◆</t>
         </is>
       </c>
-      <c r="M15" s="13" t="n"/>
-      <c r="N15" s="13" t="n"/>
-      <c r="O15" s="13" t="n"/>
-      <c r="P15" s="15" t="inlineStr">
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="n"/>
+      <c r="P15" s="15" t="n"/>
+      <c r="Q15" s="17" t="inlineStr">
         <is>
           <t>CGRP●</t>
         </is>
       </c>
-      <c r="Q15" s="13" t="n"/>
-      <c r="R15" s="13" t="n"/>
-      <c r="S15" s="13" t="n"/>
-      <c r="T15" s="13" t="n"/>
-      <c r="U15" s="13" t="n"/>
-      <c r="V15" s="13" t="n"/>
-      <c r="W15" s="13" t="n"/>
+      <c r="R15" s="15" t="n"/>
+      <c r="S15" s="15" t="n"/>
+      <c r="T15" s="15" t="n"/>
+      <c r="U15" s="15" t="n"/>
+      <c r="V15" s="15" t="n"/>
+      <c r="W15" s="15" t="n"/>
+      <c r="X15" s="15" t="n"/>
     </row>
     <row r="16" ht="47" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>13 Bristol Myers Squibb · 🇺🇸 BMY</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">3★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>CTLA-4★
 PD-1●
 LAG-3★</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr">
         <is>
           <t>BCMA/CD19 CAR-T●</t>
         </is>
       </c>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>TYK2★</t>
         </is>
       </c>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="13" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
-      <c r="Q16" s="13" t="n"/>
-      <c r="R16" s="13" t="n"/>
-      <c r="S16" s="13" t="n"/>
-      <c r="T16" s="13" t="n"/>
-      <c r="U16" s="13" t="n"/>
-      <c r="V16" s="13" t="n"/>
-      <c r="W16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="15" t="n"/>
+      <c r="S16" s="15" t="n"/>
+      <c r="T16" s="15" t="n"/>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="n"/>
+      <c r="W16" s="15" t="n"/>
+      <c r="X16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="47" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>14 Vertex · 🇺🇸 VRTX</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1524,671 +1970,1232 @@
           </r>
         </is>
       </c>
-      <c r="Q17" s="13" t="n"/>
-      <c r="R17" s="13" t="n"/>
-      <c r="S17" s="14" t="inlineStr">
+      <c r="R17" s="15" t="n"/>
+      <c r="S17" s="15" t="n"/>
+      <c r="T17" s="16" t="inlineStr">
         <is>
           <t>CFTR◆</t>
         </is>
       </c>
-      <c r="T17" s="13" t="n"/>
-      <c r="U17" s="13" t="n"/>
-      <c r="V17" s="12" t="inlineStr">
+      <c r="U17" s="15" t="n"/>
+      <c r="V17" s="15" t="n"/>
+      <c r="W17" s="14" t="inlineStr">
         <is>
           <t>CRISPR/BCL11A★</t>
         </is>
       </c>
-      <c r="W17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="X17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="47" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>15 Sanofi · 🇫🇷 SNY</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="17" t="inlineStr">
         <is>
           <t>CD38●</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>IL-4/13◆</t>
         </is>
       </c>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
-      <c r="L18" s="13" t="n"/>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="16" t="inlineStr">
         <is>
           <t>基础胰岛素◆</t>
         </is>
       </c>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
-      <c r="Q18" s="13" t="n"/>
-      <c r="R18" s="13" t="n"/>
-      <c r="S18" s="12" t="inlineStr">
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="14" t="inlineStr">
         <is>
           <t>溶酶体酶替代★</t>
         </is>
       </c>
-      <c r="T18" s="16" t="inlineStr">
+      <c r="U18" s="18" t="inlineStr">
         <is>
           <t>抗凝血酶○</t>
         </is>
       </c>
-      <c r="U18" s="13" t="n"/>
-      <c r="V18" s="13" t="n"/>
-      <c r="W18" s="13" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="V18" s="15" t="n"/>
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="47" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>16 GSK · 🇬🇧 GSK</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>PD-1●</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>BCMA-ADC●</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>IL-5●</t>
         </is>
       </c>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="13" t="n"/>
-      <c r="V19" s="13" t="n"/>
-      <c r="W19" s="13" t="n"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+      <c r="R19" s="15" t="n"/>
+      <c r="S19" s="15" t="n"/>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="15" t="n"/>
+      <c r="V19" s="15" t="n"/>
+      <c r="W19" s="15" t="n"/>
+      <c r="X19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="47" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>17 Chugai（罗氏系）· 🇯🇵 4519</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>IL-6★</t>
         </is>
       </c>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
-      <c r="L20" s="13" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
-      <c r="Q20" s="13" t="n"/>
-      <c r="R20" s="13" t="n"/>
-      <c r="S20" s="13" t="n"/>
-      <c r="T20" s="13" t="n"/>
-      <c r="U20" s="12" t="inlineStr">
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="15" t="n"/>
+      <c r="S20" s="15" t="n"/>
+      <c r="T20" s="15" t="n"/>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="14" t="inlineStr">
         <is>
           <t>血友病·双抗★</t>
         </is>
       </c>
-      <c r="V20" s="13" t="n"/>
-      <c r="W20" s="13" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="W20" s="15" t="n"/>
+      <c r="X20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="47" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>18 Merck KGaA · 🇩🇪 MRK.DE</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>EGFR★</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>PD-L1●</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
-      <c r="L21" s="13" t="n"/>
-      <c r="M21" s="13" t="n"/>
-      <c r="N21" s="13" t="n"/>
-      <c r="O21" s="15" t="inlineStr">
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t>MS●</t>
         </is>
       </c>
-      <c r="P21" s="13" t="n"/>
-      <c r="Q21" s="13" t="n"/>
-      <c r="R21" s="13" t="n"/>
-      <c r="S21" s="13" t="n"/>
-      <c r="T21" s="13" t="n"/>
-      <c r="U21" s="13" t="n"/>
-      <c r="V21" s="13" t="n"/>
-      <c r="W21" s="13" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n"/>
+      <c r="W21" s="15" t="n"/>
+      <c r="X21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="47" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>19 Regeneron · 🇺🇸 REGN</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="17" t="inlineStr">
         <is>
           <t>PD-1●</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr">
         <is>
           <t>BCMA/CD20双抗●</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>IL-4/13◆</t>
         </is>
       </c>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
-      <c r="L22" s="15" t="inlineStr">
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="17" t="inlineStr">
         <is>
           <t>PCSK9●</t>
         </is>
       </c>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="13" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="13" t="n"/>
-      <c r="Q22" s="13" t="n"/>
-      <c r="R22" s="13" t="n"/>
-      <c r="S22" s="13" t="n"/>
-      <c r="T22" s="13" t="n"/>
-      <c r="U22" s="13" t="n"/>
-      <c r="V22" s="13" t="n"/>
-      <c r="W22" s="13" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="15" t="n"/>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
+      <c r="U22" s="15" t="n"/>
+      <c r="V22" s="15" t="n"/>
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="47" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>20 UCB · 🇧🇪 UCB</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>IL-17A/F★
 TNF●</t>
         </is>
       </c>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="17" t="inlineStr">
         <is>
           <t>FcRn●</t>
         </is>
       </c>
-      <c r="L23" s="13" t="n"/>
-      <c r="M23" s="13" t="n"/>
-      <c r="N23" s="13" t="n"/>
-      <c r="O23" s="13" t="n"/>
-      <c r="P23" s="13" t="n"/>
-      <c r="Q23" s="13" t="n"/>
-      <c r="R23" s="12" t="inlineStr">
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="15" t="n"/>
+      <c r="S23" s="14" t="inlineStr">
         <is>
           <t>SV2A★</t>
         </is>
       </c>
-      <c r="S23" s="13" t="n"/>
-      <c r="T23" s="13" t="n"/>
-      <c r="U23" s="13" t="n"/>
-      <c r="V23" s="13" t="n"/>
-      <c r="W23" s="15" t="inlineStr">
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="15" t="n"/>
+      <c r="V23" s="15" t="n"/>
+      <c r="W23" s="15" t="n"/>
+      <c r="X23" s="17" t="inlineStr">
         <is>
           <t>硬骨素·骨●</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="24" ht="47" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>21 argenx · 🇳🇱 ARGX</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="13" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>FcRn★</t>
         </is>
       </c>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="13" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="13" t="n"/>
-      <c r="Q24" s="13" t="n"/>
-      <c r="R24" s="13" t="n"/>
-      <c r="S24" s="13" t="n"/>
-      <c r="T24" s="13" t="n"/>
-      <c r="U24" s="13" t="n"/>
-      <c r="V24" s="13" t="n"/>
-      <c r="W24" s="13" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="15" t="n"/>
+      <c r="S24" s="15" t="n"/>
+      <c r="T24" s="15" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15" t="n"/>
+      <c r="W24" s="15" t="n"/>
+      <c r="X24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="47" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>22 Galderma · 🇨🇭 GALD</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="13" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="12" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>IL-31★</t>
         </is>
       </c>
-      <c r="K25" s="13" t="n"/>
-      <c r="L25" s="13" t="n"/>
-      <c r="M25" s="13" t="n"/>
-      <c r="N25" s="13" t="n"/>
-      <c r="O25" s="13" t="n"/>
-      <c r="P25" s="13" t="n"/>
-      <c r="Q25" s="13" t="n"/>
-      <c r="R25" s="13" t="n"/>
-      <c r="S25" s="13" t="n"/>
-      <c r="T25" s="13" t="n"/>
-      <c r="U25" s="13" t="n"/>
-      <c r="V25" s="13" t="n"/>
-      <c r="W25" s="13" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="15" t="n"/>
+      <c r="N25" s="15" t="n"/>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="15" t="n"/>
+      <c r="Q25" s="15" t="n"/>
+      <c r="R25" s="15" t="n"/>
+      <c r="S25" s="15" t="n"/>
+      <c r="T25" s="15" t="n"/>
+      <c r="U25" s="15" t="n"/>
+      <c r="V25" s="15" t="n"/>
+      <c r="W25" s="15" t="n"/>
+      <c r="X25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="47" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>24 Takeda · 🇯🇵 TAK</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>蛋白酶体★</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="15" t="inlineStr">
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="17" t="inlineStr">
         <is>
           <t>CD30-ADC●</t>
         </is>
       </c>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="12" t="inlineStr">
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="15" t="n"/>
+      <c r="K26" s="14" t="inlineStr">
         <is>
           <t>α4β7★</t>
         </is>
       </c>
-      <c r="K26" s="13" t="n"/>
-      <c r="L26" s="13" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
-      <c r="Q26" s="13" t="n"/>
-      <c r="R26" s="13" t="n"/>
-      <c r="S26" s="15" t="inlineStr">
+      <c r="L26" s="15" t="n"/>
+      <c r="M26" s="15" t="n"/>
+      <c r="N26" s="15" t="n"/>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="15" t="n"/>
+      <c r="Q26" s="15" t="n"/>
+      <c r="R26" s="15" t="n"/>
+      <c r="S26" s="15" t="n"/>
+      <c r="T26" s="17" t="inlineStr">
         <is>
           <t>溶酶体酶替代●</t>
         </is>
       </c>
-      <c r="T26" s="15" t="inlineStr">
+      <c r="U26" s="17" t="inlineStr">
         <is>
           <t>HAE激肽●</t>
         </is>
       </c>
-      <c r="U26" s="13" t="n"/>
-      <c r="V26" s="13" t="n"/>
-      <c r="W26" s="13" t="n"/>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="V26" s="15" t="n"/>
+      <c r="W26" s="15" t="n"/>
+      <c r="X26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="47" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>25 江苏恒瑞 · 🇨🇳 600276</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>VEGFR2●
 HER2●</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>PD-1●</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>HER2-ADC○</t>
         </is>
       </c>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
-      <c r="L27" s="13" t="n"/>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="15" t="n"/>
+      <c r="L27" s="15" t="n"/>
+      <c r="M27" s="15" t="n"/>
+      <c r="N27" s="18" t="inlineStr">
         <is>
           <t>GLP-1○</t>
         </is>
       </c>
-      <c r="N27" s="13" t="n"/>
-      <c r="O27" s="13" t="n"/>
-      <c r="P27" s="13" t="n"/>
-      <c r="Q27" s="13" t="n"/>
-      <c r="R27" s="13" t="n"/>
-      <c r="S27" s="13" t="n"/>
-      <c r="T27" s="13" t="n"/>
-      <c r="U27" s="13" t="n"/>
-      <c r="V27" s="13" t="n"/>
-      <c r="W27" s="13" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="15" t="n"/>
+      <c r="Q27" s="15" t="n"/>
+      <c r="R27" s="15" t="n"/>
+      <c r="S27" s="15" t="n"/>
+      <c r="T27" s="15" t="n"/>
+      <c r="U27" s="15" t="n"/>
+      <c r="V27" s="15" t="n"/>
+      <c r="W27" s="15" t="n"/>
+      <c r="X27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="47" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>26 Sun Pharma · 🇮🇳 SUNP</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>IL-23●</t>
         </is>
       </c>
-      <c r="I28" s="15" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>JAK●</t>
         </is>
       </c>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
-      <c r="L28" s="13" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
-      <c r="Q28" s="13" t="n"/>
-      <c r="R28" s="13" t="n"/>
-      <c r="S28" s="13" t="n"/>
-      <c r="T28" s="13" t="n"/>
-      <c r="U28" s="13" t="n"/>
-      <c r="V28" s="13" t="n"/>
-      <c r="W28" s="13" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="K28" s="15" t="n"/>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="n"/>
+      <c r="N28" s="15" t="n"/>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="15" t="n"/>
+      <c r="Q28" s="15" t="n"/>
+      <c r="R28" s="15" t="n"/>
+      <c r="S28" s="15" t="n"/>
+      <c r="T28" s="15" t="n"/>
+      <c r="U28" s="15" t="n"/>
+      <c r="V28" s="15" t="n"/>
+      <c r="W28" s="15" t="n"/>
+      <c r="X28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="47" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>28 Bayer · 🇩🇪 BAYN</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>2●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>多激酶●</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="15" t="inlineStr">
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>放射 Ra-223●</t>
         </is>
       </c>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
-      <c r="L29" s="13" t="n"/>
-      <c r="M29" s="13" t="n"/>
-      <c r="N29" s="13" t="n"/>
-      <c r="O29" s="13" t="n"/>
-      <c r="P29" s="13" t="n"/>
-      <c r="Q29" s="13" t="n"/>
-      <c r="R29" s="13" t="n"/>
-      <c r="S29" s="13" t="n"/>
-      <c r="T29" s="13" t="n"/>
-      <c r="U29" s="13" t="n"/>
-      <c r="V29" s="13" t="n"/>
-      <c r="W29" s="12" t="inlineStr">
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="15" t="n"/>
+      <c r="L29" s="15" t="n"/>
+      <c r="M29" s="15" t="n"/>
+      <c r="N29" s="15" t="n"/>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="15" t="n"/>
+      <c r="Q29" s="15" t="n"/>
+      <c r="R29" s="15" t="n"/>
+      <c r="S29" s="15" t="n"/>
+      <c r="T29" s="15" t="n"/>
+      <c r="U29" s="15" t="n"/>
+      <c r="V29" s="15" t="n"/>
+      <c r="W29" s="15" t="n"/>
+      <c r="X29" s="14" t="inlineStr">
         <is>
           <t>非甾体MRA·肾★</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="30" ht="47" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>29 Alnylam · 🇺🇸 ALNY</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
-      <c r="L30" s="15" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>PCSK9●</t>
         </is>
       </c>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="13" t="n"/>
-      <c r="R30" s="13" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="14" t="inlineStr">
+      <c r="N30" s="15" t="n"/>
+      <c r="O30" s="15" t="n"/>
+      <c r="P30" s="15" t="n"/>
+      <c r="Q30" s="15" t="n"/>
+      <c r="R30" s="15" t="n"/>
+      <c r="S30" s="15" t="n"/>
+      <c r="T30" s="15" t="n"/>
+      <c r="U30" s="16" t="inlineStr">
         <is>
           <t>TTR/卟啉/草酸◆</t>
         </is>
       </c>
-      <c r="U30" s="13" t="n"/>
-      <c r="V30" s="13" t="n"/>
-      <c r="W30" s="13" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="V30" s="15" t="n"/>
+      <c r="W30" s="15" t="n"/>
+      <c r="X30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="47" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>30 Teva · 🇮🇱 TEVA</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
-      <c r="L31" s="13" t="n"/>
-      <c r="M31" s="13" t="n"/>
-      <c r="N31" s="13" t="n"/>
-      <c r="O31" s="15" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>3●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n"/>
+      <c r="M31" s="15" t="n"/>
+      <c r="N31" s="15" t="n"/>
+      <c r="O31" s="15" t="n"/>
+      <c r="P31" s="17" t="inlineStr">
         <is>
           <t>MS●</t>
         </is>
       </c>
-      <c r="P31" s="15" t="inlineStr">
+      <c r="Q31" s="17" t="inlineStr">
         <is>
           <t>CGRP●</t>
         </is>
       </c>
-      <c r="Q31" s="15" t="inlineStr">
+      <c r="R31" s="17" t="inlineStr">
         <is>
           <t>VMAT2●</t>
         </is>
       </c>
-      <c r="R31" s="13" t="n"/>
-      <c r="S31" s="13" t="n"/>
-      <c r="T31" s="13" t="n"/>
-      <c r="U31" s="13" t="n"/>
-      <c r="V31" s="13" t="n"/>
-      <c r="W31" s="13" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="S31" s="15" t="n"/>
+      <c r="T31" s="15" t="n"/>
+      <c r="U31" s="15" t="n"/>
+      <c r="V31" s="15" t="n"/>
+      <c r="W31" s="15" t="n"/>
+      <c r="X31" s="15" t="n"/>
+    </row>
+    <row r="32" ht="47" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>31 Otsuka · 🇯🇵 4578</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="13" t="n"/>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="13" t="n"/>
-      <c r="L32" s="13" t="n"/>
-      <c r="M32" s="13" t="n"/>
-      <c r="N32" s="13" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">2★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
+      <c r="M32" s="15" t="n"/>
+      <c r="N32" s="15" t="n"/>
+      <c r="O32" s="15" t="n"/>
+      <c r="P32" s="15" t="n"/>
+      <c r="Q32" s="15" t="n"/>
+      <c r="R32" s="14" t="inlineStr">
         <is>
           <t>D2部分激动★</t>
         </is>
       </c>
-      <c r="R32" s="13" t="n"/>
-      <c r="S32" s="13" t="n"/>
-      <c r="T32" s="13" t="n"/>
-      <c r="U32" s="13" t="n"/>
-      <c r="V32" s="13" t="n"/>
-      <c r="W32" s="12" t="inlineStr">
+      <c r="S32" s="15" t="n"/>
+      <c r="T32" s="15" t="n"/>
+      <c r="U32" s="15" t="n"/>
+      <c r="V32" s="15" t="n"/>
+      <c r="W32" s="15" t="n"/>
+      <c r="X32" s="14" t="inlineStr">
         <is>
           <t>V2·多囊肾★</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="33" ht="47" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>32 Sandoz · 🇨🇭 SDZ</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="13" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="13" t="n"/>
-      <c r="O33" s="13" t="n"/>
-      <c r="P33" s="13" t="n"/>
-      <c r="Q33" s="13" t="n"/>
-      <c r="R33" s="13" t="n"/>
-      <c r="S33" s="13" t="n"/>
-      <c r="T33" s="13" t="n"/>
-      <c r="U33" s="13" t="n"/>
-      <c r="V33" s="13" t="n"/>
-      <c r="W33" s="13" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="15" t="n"/>
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="15" t="n"/>
+      <c r="O33" s="15" t="n"/>
+      <c r="P33" s="15" t="n"/>
+      <c r="Q33" s="15" t="n"/>
+      <c r="R33" s="15" t="n"/>
+      <c r="S33" s="15" t="n"/>
+      <c r="T33" s="15" t="n"/>
+      <c r="U33" s="15" t="n"/>
+      <c r="V33" s="15" t="n"/>
+      <c r="W33" s="15" t="n"/>
+      <c r="X33" s="15" t="n"/>
+    </row>
+    <row r="34" ht="47" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>33 Revolution Med. · 🇺🇸 RVMD</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00B0682C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">1★
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">0◆
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="006E7C74"/>
+              <sz val="9"/>
+            </rPr>
+            <t>0●</t>
+          </r>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2209,78 +3216,79 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="13" t="n"/>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="13" t="n"/>
-      <c r="L34" s="13" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
-      <c r="Q34" s="13" t="n"/>
-      <c r="R34" s="13" t="n"/>
-      <c r="S34" s="13" t="n"/>
-      <c r="T34" s="13" t="n"/>
-      <c r="U34" s="13" t="n"/>
-      <c r="V34" s="13" t="n"/>
-      <c r="W34" s="13" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="15" t="n"/>
+      <c r="L34" s="15" t="n"/>
+      <c r="M34" s="15" t="n"/>
+      <c r="N34" s="15" t="n"/>
+      <c r="O34" s="15" t="n"/>
+      <c r="P34" s="15" t="n"/>
+      <c r="Q34" s="15" t="n"/>
+      <c r="R34" s="15" t="n"/>
+      <c r="S34" s="15" t="n"/>
+      <c r="T34" s="15" t="n"/>
+      <c r="U34" s="15" t="n"/>
+      <c r="V34" s="15" t="n"/>
+      <c r="W34" s="15" t="n"/>
+      <c r="X34" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>口径说明：</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>· 每个格子里，同一公司在该通路上的多个靶点已各自单独成行。</t>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>· 「★◆●计数」= 该公司在全部通路上 ★首创 / ◆领跑 / ●重要 的靶点数量合计。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟的前沿：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>· 仅标注有重大布局的靶点（非全管线）；通路列沿用本站「通路词典」的分区。</t>
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>· 不属于这些通路组的重磅（疫苗 / HIV·HCV / 抗凝 / 眼科VEGF / 前列腺激素 / EPO·G-CSF / 骨·医美）未在表中，详见「公司词典」。</t>
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>· 已剔除市值榜中的非研发型公司：CVS Health(第12·PBM)、WuXi药明康德(第23·CRO)、Lonza(第27·CDMO)；Sandoz为生物类似药商，整行留空。</t>
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商，整行留空。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="H3:K3"/>
+  <mergeCells count="7">
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="S3:W3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="T3:X3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -1209,17 +1209,7 @@
               <color rgb="003C6E64"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1◆</t>
           </r>
         </is>
       </c>
@@ -1449,16 +1439,6 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -1692,17 +1672,7 @@
               <color rgb="003C6E64"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1◆</t>
           </r>
         </is>
       </c>
@@ -1842,16 +1812,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
@@ -1921,17 +1881,7 @@
               <color rgb="003C6E64"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1◆</t>
           </r>
         </is>
       </c>
@@ -2080,26 +2030,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
@@ -2157,27 +2087,7 @@
               <color rgb="00B0682C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">2★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>2★</t>
           </r>
         </is>
       </c>
@@ -2234,16 +2144,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
@@ -2294,16 +2194,6 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2386,16 +2276,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
@@ -2458,27 +2338,7 @@
               <color rgb="00B0682C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1★</t>
           </r>
         </is>
       </c>
@@ -2524,27 +2384,7 @@
               <color rgb="00B0682C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1★</t>
           </r>
         </is>
       </c>
@@ -2597,16 +2437,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
@@ -2665,26 +2495,6 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2744,26 +2554,6 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2822,16 +2612,6 @@
               <sz val="9"/>
             </rPr>
             <t xml:space="preserve">1★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
 </t>
           </r>
           <r>
@@ -2892,16 +2672,6 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
               <color rgb="003C6E64"/>
               <sz val="9"/>
             </rPr>
@@ -2958,26 +2728,6 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -3039,27 +2789,7 @@
               <color rgb="00B0682C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">2★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>2★</t>
           </r>
         </is>
       </c>
@@ -3100,39 +2830,7 @@
           <t>32 Sandoz · 🇨🇭 SDZ</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00B0682C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
-          </r>
-        </is>
-      </c>
+      <c r="B33" s="13" t="n"/>
       <c r="C33" s="15" t="n"/>
       <c r="D33" s="15" t="n"/>
       <c r="E33" s="15" t="n"/>
@@ -3171,27 +2869,7 @@
               <color rgb="00B0682C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">1★
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="003C6E64"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">0◆
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="006E7C74"/>
-              <sz val="9"/>
-            </rPr>
-            <t>0●</t>
+            <t>1★</t>
           </r>
         </is>
       </c>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2916,43 +2916,161 @@
       <c r="W34" s="15" t="n"/>
       <c r="X34" s="15" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="35" ht="47" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>补 Moderna · 🇺🇸 MRNA</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="15" t="n"/>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="n"/>
+      <c r="M35" s="15" t="n"/>
+      <c r="N35" s="15" t="n"/>
+      <c r="O35" s="15" t="n"/>
+      <c r="P35" s="15" t="n"/>
+      <c r="Q35" s="15" t="n"/>
+      <c r="R35" s="15" t="n"/>
+      <c r="S35" s="15" t="n"/>
+      <c r="T35" s="18" t="inlineStr">
+        <is>
+          <t>mRNA蛋白替代○</t>
+        </is>
+      </c>
+      <c r="U35" s="15" t="n"/>
+      <c r="V35" s="15" t="n"/>
+      <c r="W35" s="15" t="n"/>
+      <c r="X35" s="15" t="n"/>
+    </row>
+    <row r="36" ht="47" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>补 BioNTech · 🇩🇪 BNTX</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>PD-L1×VEGF双抗○</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>ADC/CAR-T○</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="15" t="n"/>
+      <c r="K36" s="15" t="n"/>
+      <c r="L36" s="15" t="n"/>
+      <c r="M36" s="15" t="n"/>
+      <c r="N36" s="15" t="n"/>
+      <c r="O36" s="15" t="n"/>
+      <c r="P36" s="15" t="n"/>
+      <c r="Q36" s="15" t="n"/>
+      <c r="R36" s="15" t="n"/>
+      <c r="S36" s="15" t="n"/>
+      <c r="T36" s="15" t="n"/>
+      <c r="U36" s="15" t="n"/>
+      <c r="V36" s="15" t="n"/>
+      <c r="W36" s="15" t="n"/>
+      <c r="X36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="47" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>补 Legend Biotech · 🇺🇸 LEGN</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="003C6E64"/>
+              <sz val="9"/>
+            </rPr>
+            <t>1◆</t>
+          </r>
+        </is>
+      </c>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>BCMA CAR-T◆</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="15" t="n"/>
+      <c r="L37" s="15" t="n"/>
+      <c r="M37" s="15" t="n"/>
+      <c r="N37" s="15" t="n"/>
+      <c r="O37" s="15" t="n"/>
+      <c r="P37" s="15" t="n"/>
+      <c r="Q37" s="15" t="n"/>
+      <c r="R37" s="15" t="n"/>
+      <c r="S37" s="15" t="n"/>
+      <c r="T37" s="15" t="n"/>
+      <c r="U37" s="15" t="n"/>
+      <c r="V37" s="15" t="n"/>
+      <c r="W37" s="15" t="n"/>
+      <c r="X37" s="15" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>口径说明：</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>· 「★◆●计数」= 该公司在全部通路上 ★首创 / ◆领跑 / ●重要 的靶点数量合计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
+          <t>· 「★◆●计数」= 该公司在全部通路上 ★首创 / ◆领跑 / ●重要 的靶点数量合计。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商，整行留空。</t>
         </is>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>表面投送/ADC/CAR-T</t>
+          <t>表面投送 ADC/CAR-T/双抗</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
@@ -982,7 +982,7 @@
               <color rgb="002E463E"/>
               <sz val="8.5"/>
             </rPr>
-            <t>◆</t>
+            <t>×CD3◆</t>
           </r>
         </is>
       </c>
@@ -1048,7 +1048,7 @@
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
-            <t>3●</t>
+            <t>4●</t>
           </r>
         </is>
       </c>
@@ -1065,7 +1065,11 @@
       </c>
       <c r="F7" s="15" t="n"/>
       <c r="G7" s="15" t="n"/>
-      <c r="H7" s="15" t="n"/>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>CD20×CD3●</t>
+        </is>
+      </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
           <t>TNF◆
@@ -1131,7 +1135,7 @@
               <color rgb="006E7C74"/>
               <sz val="9"/>
             </rPr>
-            <t>3●</t>
+            <t>4●</t>
           </r>
         </is>
       </c>
@@ -1152,6 +1156,7 @@
       <c r="H8" s="14" t="inlineStr">
         <is>
           <t>CD20★
+CD20×CD3●
 HER2-ADC●</t>
         </is>
       </c>
@@ -1592,7 +1597,7 @@
               <color rgb="002E463E"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">CD19-BiTE★
+            <t xml:space="preserve">CD19×CD3 BiTE★
 </t>
           </r>
           <r>
@@ -1758,7 +1763,7 @@
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>BCMA●</t>
+          <t>BCMA×CD3●</t>
         </is>
       </c>
       <c r="I15" s="15" t="n"/>
@@ -3051,26 +3056,33 @@
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
+          <t>· CAR-T、CD3双抗(T细胞衔接器)都是把免疫细胞重定向到表面抗原的模态，统一归入「表面投送 ADC/CAR-T/双抗」列，按其靶向的表面抗原(CD19/BCMA/CD20…)填格；CD3只是效应臂，非疾病靶点。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
+          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商，整行留空。</t>
         </is>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X45"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -625,7 +625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>横=通路组 · 纵=市值前30家药企 · 公司后设「★◆●计数」列 · 每格每个靶点单独一行 ｜ ★首创FIC ◆领跑BIC ●重要 ○在研 ｜ 红色加粗=最热但未攻克前沿 ｜ 市值截至2026-07</t>
+          <t>横=通路组 · 纵=前30家药企(+3榜外) · 公司后设★◆●计数列 · 每格每靶点单独一行 ｜ ★首创 ◆领跑 ●重要 ○在研 ｜ 红色加粗=最热未攻克前沿 ｜ 蓝色=专利到期年份(≤2030) ｜ 市值截至2026-07</t>
         </is>
       </c>
     </row>
@@ -988,8 +988,32 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>IL-12/23★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>IL-12/23★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2025)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 IL-23●</t>
+          </r>
         </is>
       </c>
       <c r="J6" s="15" t="n"/>
@@ -1072,8 +1096,32 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>TNF◆
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>TNF◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2023)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 IL-23◆</t>
+          </r>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
@@ -1162,7 +1210,23 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>IL-6★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>IL-6★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2024)</t>
+          </r>
         </is>
       </c>
       <c r="J8" s="15" t="n"/>
@@ -1224,7 +1288,23 @@
       <c r="F9" s="15" t="n"/>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>PD-1◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>PD-1◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2028)</t>
+          </r>
         </is>
       </c>
       <c r="H9" s="15" t="n"/>
@@ -1240,7 +1320,23 @@
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>DPP-4★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>DPP-4★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2026)</t>
+          </r>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -1315,8 +1411,32 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>IL-17★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>IL-17★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2029)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 IL-1β●</t>
+          </r>
         </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
@@ -1394,7 +1514,23 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>PARP◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>PARP◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2028)</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="15" t="n"/>
@@ -1422,7 +1558,23 @@
       <c r="M11" s="15" t="n"/>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>SGLT2◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>SGLT2◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2025)</t>
+          </r>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -1621,7 +1773,23 @@
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>TNF●</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>TNF●</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2029)</t>
+          </r>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
@@ -1633,7 +1801,23 @@
       <c r="L13" s="15" t="n"/>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>PCSK9◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>PCSK9◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2028)</t>
+          </r>
         </is>
       </c>
       <c r="N13" s="15" t="n"/>
@@ -1756,7 +1940,23 @@
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>CDK4/6★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>CDK4/6★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2027)</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="15" t="n"/>
@@ -1769,7 +1969,23 @@
       <c r="I15" s="15" t="n"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>JAK★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>JAK★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2025)</t>
+          </r>
         </is>
       </c>
       <c r="K15" s="15" t="n"/>
@@ -1830,9 +2046,33 @@
       <c r="F16" s="15" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>CTLA-4★
-PD-1●
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>CTLA-4★
+PD-1●</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2028)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 LAG-3★</t>
+          </r>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -2104,7 +2344,23 @@
       <c r="H20" s="15" t="n"/>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>IL-6★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>IL-6★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002F6FB0"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2024)</t>
+          </r>
         </is>
       </c>
       <c r="J20" s="15" t="n"/>
@@ -3049,42 +3305,49 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>· 「★◆●计数」= 该公司在全部通路上 ★首创 / ◆领跑 / ●重要 的靶点数量合计。</t>
+          <t>· 蓝色年份=该靶点代表药的美国专利/独占到期年份(近似,≤2030近期悬崖;随剂型/诉讼变动)。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="20" t="inlineStr">
         <is>
-          <t>· CAR-T、CD3双抗(T细胞衔接器)都是把免疫细胞重定向到表面抗原的模态，统一归入「表面投送 ADC/CAR-T/双抗」列，按其靶向的表面抗原(CD19/BCMA/CD20…)填格；CD3只是效应臂，非疾病靶点。</t>
+          <t>· 「★◆●计数」= 该公司在全部通路上 ★首创 / ◆领跑 / ●重要 的靶点数量合计。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="20" t="inlineStr">
         <is>
-          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
+          <t>· CAR-T、CD3双抗(T细胞衔接器)都是把免疫细胞重定向到表面抗原的模态，统一归入「表面投送 ADC/CAR-T/双抗」列，按其靶向的表面抗原(CD19/BCMA/CD20…)填格；CD3只是效应臂，非疾病靶点。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>· 仅标注有重大布局的靶点（非全管线）；不属于这些通路组的重磅（疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美）见「公司词典」。</t>
+          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商，整行留空。</t>
+          <t>· 仅标注有重大布局的靶点(非全管线)；不属于这些通路组的重磅(疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美)见「公司词典」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商整行留空；末尾3家(Moderna/BioNTech/Legend)为榜外补充。</t>
         </is>
       </c>
     </row>

--- a/公司x通路矩阵.xlsx
+++ b/公司x通路矩阵.xlsx
@@ -586,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -625,7 +625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>横=通路组 · 纵=前30家药企(+3榜外) · 公司后设★◆●计数列 · 每格每靶点单独一行 ｜ ★首创 ◆领跑 ●重要 ○在研 ｜ 红色加粗=最热未攻克前沿 ｜ 蓝色=专利到期年份(≤2030) ｜ 市值截至2026-07</t>
+          <t>★首创 ◆领跑 ●重要 ○在研 ｜ 红色加粗=最热未攻克前沿 ｜ 绿色年份=专利已过期(≤2025) 蓝色年份=即将到期(2026–2030) ｜ 市值截至2026-07</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2025)</t>
@@ -1108,7 +1108,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2023)</t>
@@ -1189,8 +1189,32 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>HER2★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>HER2★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2019)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 BRAF●</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="15" t="n"/>
@@ -1203,9 +1227,33 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>CD20★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>CD20★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2019)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 CD20×CD3●
 HER2-ADC●</t>
+          </r>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1222,7 +1270,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2024)</t>
@@ -1314,8 +1362,32 @@
       <c r="L9" s="15" t="n"/>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>他汀★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>他汀★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2006)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 口服PCSK9○</t>
+          </r>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
@@ -1391,8 +1463,32 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>BCR-ABL★
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>BCR-ABL★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2015)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t xml:space="preserve">
 BRAF/MEK●</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="15" t="n"/>
@@ -1441,7 +1537,23 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>S1P●</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>S1P●</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2019)</t>
+          </r>
         </is>
       </c>
       <c r="K10" s="15" t="n"/>
@@ -1570,7 +1682,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2025)</t>
@@ -1981,7 +2093,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2025)</t>
@@ -1992,7 +2104,23 @@
       <c r="L15" s="15" t="n"/>
       <c r="M15" s="16" t="inlineStr">
         <is>
-          <t>他汀◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>他汀◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2011)</t>
+          </r>
         </is>
       </c>
       <c r="N15" s="15" t="n"/>
@@ -2241,7 +2369,23 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>基础胰岛素◆</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>基础胰岛素◆</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2016)</t>
+          </r>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -2356,7 +2500,7 @@
             <rPr>
               <rFont val="Arial"/>
               <b val="1"/>
-              <color rgb="002F6FB0"/>
+              <color rgb="002E8B57"/>
               <sz val="8.5"/>
             </rPr>
             <t>(2024)</t>
@@ -2414,7 +2558,23 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>EGFR★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>EGFR★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2016)</t>
+          </r>
         </is>
       </c>
       <c r="D21" s="15" t="n"/>
@@ -2709,7 +2869,23 @@
       <c r="D26" s="15" t="n"/>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>蛋白酶体★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>蛋白酶体★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2022)</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="15" t="n"/>
@@ -2888,7 +3064,23 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>多激酶●</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>多激酶●</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2020)</t>
+          </r>
         </is>
       </c>
       <c r="D29" s="15" t="n"/>
@@ -3015,7 +3207,23 @@
       <c r="O31" s="15" t="n"/>
       <c r="P31" s="17" t="inlineStr">
         <is>
-          <t>MS●</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>MS●</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2017)</t>
+          </r>
         </is>
       </c>
       <c r="Q31" s="17" t="inlineStr">
@@ -3071,7 +3279,23 @@
       <c r="Q32" s="15" t="n"/>
       <c r="R32" s="14" t="inlineStr">
         <is>
-          <t>D2部分激动★</t>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="002E463E"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>D2部分激动★</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="002E8B57"/>
+              <sz val="8.5"/>
+            </rPr>
+            <t>(2015)</t>
+          </r>
         </is>
       </c>
       <c r="S32" s="15" t="n"/>
@@ -3305,7 +3529,7 @@
     <row r="40">
       <c r="A40" s="20" t="inlineStr">
         <is>
-          <t>· 蓝色年份=该靶点代表药的美国专利/独占到期年份(近似,≤2030近期悬崖;随剂型/诉讼变动)。</t>
+          <t>· 年份=代表药美国专利/独占到期年份(近似)：绿色=已过期(≤2025)，蓝色=即将到期(2026–2030)；随剂型/诉讼变动。</t>
         </is>
       </c>
     </row>
@@ -3326,28 +3550,21 @@
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
         <is>
-          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行。</t>
+          <t>· 每个格子里同一公司在该通路的多个靶点各自单独成行；红色加粗=当下最热但尚未攻克/未成熟(KRAS/Lp(a)/amylin/DLL3/GPRC5D/Nav1.8)。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>· 红色加粗靶点 = 当下最热但尚未攻克/未成熟：KRAS(G12C/G12D/pan-RAS)、Lp(a)、amylin、DLL3、GPRC5D、Nav1.8。</t>
+          <t>· 仅标注有重大布局的靶点(非全管线)；不属于这些通路组的重磅(疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美)见「公司词典」。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="inlineStr">
         <is>
-          <t>· 仅标注有重大布局的靶点(非全管线)；不属于这些通路组的重磅(疫苗/HIV/抗凝/眼科VEGF/前列腺激素/EPO·G-CSF/骨·医美)见「公司词典」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz为生物类似药商整行留空；末尾3家(Moderna/BioNTech/Legend)为榜外补充。</t>
+          <t>· 已剔除非研发型：CVS(PBM)、WuXi(CRO)、Lonza(CDMO)；Sandoz整行留空；末尾3家(Moderna/BioNTech/Legend)为榜外补充。</t>
         </is>
       </c>
     </row>
